--- a/artfynd/A 26601-2023 artfynd.xlsx
+++ b/artfynd/A 26601-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128561689</v>
       </c>
       <c r="B2" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128561696</v>
       </c>
       <c r="B3" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26601-2023 artfynd.xlsx
+++ b/artfynd/A 26601-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128561689</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128561696</v>
       </c>
       <c r="B3" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26601-2023 artfynd.xlsx
+++ b/artfynd/A 26601-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128561689</v>
       </c>
       <c r="B2" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128561696</v>
       </c>
       <c r="B3" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26601-2023 artfynd.xlsx
+++ b/artfynd/A 26601-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128561689</v>
       </c>
       <c r="B2" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128561696</v>
       </c>
       <c r="B3" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
